--- a/LDC.xlsx
+++ b/LDC.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://icrafcifor-my.sharepoint.com/personal/d_bodro_landscapealliance_org/Documents/Documents/GitHub/RegEco-BETIBEL-SOLUSI/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{AD9C7155-FC41-450E-8731-B9FE4ACDF2E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6726F676-B4B1-4ADB-9366-FFE8D3879724}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="8_{AD9C7155-FC41-450E-8731-B9FE4ACDF2E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4BA9F572-5CAF-405B-AB55-B7F750F07592}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FDBA8644-8BAA-46FD-AFD9-3CA6C0ACD717}"/>
+    <workbookView xWindow="-28935" yWindow="-135" windowWidth="29070" windowHeight="15750" xr2:uid="{FDBA8644-8BAA-46FD-AFD9-3CA6C0ACD717}"/>
   </bookViews>
   <sheets>
     <sheet name="LDC" sheetId="1" r:id="rId1"/>
@@ -36,10 +36,6 @@
     </ext>
   </extLst>
 </workbook>
-</file>
-
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -428,10 +424,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC9CAD68-C067-4252-8930-616EED34A806}">
-  <dimension ref="A1:AA62"/>
+  <dimension ref="A1:AD62"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A1" s="1">
         <v>1</v>
       </c>
@@ -513,8 +509,17 @@
       <c r="AA1" s="1">
         <v>27</v>
       </c>
+      <c r="AB1" s="1">
+        <v>28</v>
+      </c>
+      <c r="AC1" s="1">
+        <v>29</v>
+      </c>
+      <c r="AD1" s="1">
+        <v>30</v>
+      </c>
     </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
         <v>0</v>
       </c>
@@ -596,8 +601,17 @@
       <c r="AA2" s="2">
         <v>0</v>
       </c>
+      <c r="AB2" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC2" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD2" s="2">
+        <v>0</v>
+      </c>
     </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>0</v>
       </c>
@@ -679,8 +693,17 @@
       <c r="AA3" s="2">
         <v>0</v>
       </c>
+      <c r="AB3" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC3" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD3" s="2">
+        <v>0</v>
+      </c>
     </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>0</v>
       </c>
@@ -762,8 +785,17 @@
       <c r="AA4" s="2">
         <v>0</v>
       </c>
+      <c r="AB4" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC4" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD4" s="2">
+        <v>0</v>
+      </c>
     </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>0</v>
       </c>
@@ -845,8 +877,17 @@
       <c r="AA5" s="2">
         <v>0</v>
       </c>
+      <c r="AB5" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC5" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD5" s="2">
+        <v>0</v>
+      </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>0</v>
       </c>
@@ -928,8 +969,17 @@
       <c r="AA6" s="2">
         <v>0</v>
       </c>
+      <c r="AB6" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC6" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD6" s="2">
+        <v>0</v>
+      </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>0</v>
       </c>
@@ -1011,8 +1061,17 @@
       <c r="AA7" s="2">
         <v>0</v>
       </c>
+      <c r="AB7" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC7" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD7" s="2">
+        <v>0</v>
+      </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>0</v>
       </c>
@@ -1094,8 +1153,17 @@
       <c r="AA8" s="2">
         <v>0</v>
       </c>
+      <c r="AB8" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC8" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD8" s="2">
+        <v>0</v>
+      </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <v>0</v>
       </c>
@@ -1177,8 +1245,17 @@
       <c r="AA9" s="2">
         <v>0</v>
       </c>
+      <c r="AB9" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC9" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD9" s="2">
+        <v>0</v>
+      </c>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
         <v>0</v>
       </c>
@@ -1260,8 +1337,17 @@
       <c r="AA10" s="2">
         <v>0</v>
       </c>
+      <c r="AB10" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC10" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD10" s="2">
+        <v>0</v>
+      </c>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A11" s="3">
         <v>0</v>
       </c>
@@ -1340,11 +1426,20 @@
       <c r="Z11" s="3">
         <v>0</v>
       </c>
-      <c r="AA11" s="3">
+      <c r="AA11" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB11" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC11" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD11" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A12" s="3">
         <v>0</v>
       </c>
@@ -1423,11 +1518,20 @@
       <c r="Z12" s="3">
         <v>0</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AA12" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB12" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC12" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD12" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A13" s="3">
         <v>0</v>
       </c>
@@ -1506,11 +1610,20 @@
       <c r="Z13" s="3">
         <v>0</v>
       </c>
-      <c r="AA13" s="3">
+      <c r="AA13" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB13" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC13" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD13" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A14" s="3">
         <v>0</v>
       </c>
@@ -1589,11 +1702,20 @@
       <c r="Z14" s="3">
         <v>0</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AA14" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD14" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A15" s="3">
         <v>0</v>
       </c>
@@ -1672,11 +1794,20 @@
       <c r="Z15" s="3">
         <v>0</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AA15" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB15" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC15" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD15" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A16" s="3">
         <v>0</v>
       </c>
@@ -1755,11 +1886,20 @@
       <c r="Z16" s="3">
         <v>0</v>
       </c>
-      <c r="AA16" s="3">
+      <c r="AA16" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB16" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC16" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD16" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A17" s="3">
         <v>0</v>
       </c>
@@ -1838,11 +1978,20 @@
       <c r="Z17" s="3">
         <v>0</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AA17" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB17" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC17" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD17" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A18" s="3">
         <v>0</v>
       </c>
@@ -1921,11 +2070,20 @@
       <c r="Z18" s="3">
         <v>0</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AA18" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB18" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC18" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD18" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A19" s="3">
         <v>0</v>
       </c>
@@ -2004,11 +2162,20 @@
       <c r="Z19" s="3">
         <v>0</v>
       </c>
-      <c r="AA19" s="3">
+      <c r="AA19" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB19" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC19" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD19" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A20" s="3">
         <v>0</v>
       </c>
@@ -2087,11 +2254,20 @@
       <c r="Z20" s="3">
         <v>0</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AA20" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB20" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC20" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD20" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A21" s="3">
         <v>0</v>
       </c>
@@ -2170,11 +2346,20 @@
       <c r="Z21" s="3">
         <v>0</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AA21" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB21" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC21" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD21" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A22" s="3">
         <v>0</v>
       </c>
@@ -2253,11 +2438,20 @@
       <c r="Z22" s="3">
         <v>0</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AA22" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB22" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC22" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD22" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A23" s="3">
         <v>0</v>
       </c>
@@ -2336,11 +2530,20 @@
       <c r="Z23" s="3">
         <v>0</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AA23" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB23" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC23" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD23" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A24" s="3">
         <v>0</v>
       </c>
@@ -2419,11 +2622,20 @@
       <c r="Z24" s="3">
         <v>0</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AA24" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB24" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC24" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD24" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A25" s="3">
         <v>0</v>
       </c>
@@ -2502,11 +2714,20 @@
       <c r="Z25" s="3">
         <v>0</v>
       </c>
-      <c r="AA25" s="3">
+      <c r="AA25" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB25" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC25" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD25" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A26" s="3">
         <v>0</v>
       </c>
@@ -2585,11 +2806,20 @@
       <c r="Z26" s="3">
         <v>0</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AA26" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB26" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC26" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD26" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A27" s="3">
         <v>0</v>
       </c>
@@ -2668,11 +2898,20 @@
       <c r="Z27" s="3">
         <v>0</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AA27" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB27" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC27" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD27" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A28" s="3">
         <v>0</v>
       </c>
@@ -2751,11 +2990,20 @@
       <c r="Z28" s="3">
         <v>0</v>
       </c>
-      <c r="AA28" s="3">
+      <c r="AA28" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB28" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC28" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD28" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A29" s="3">
         <v>0</v>
       </c>
@@ -2834,11 +3082,20 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AA29" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB29" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC29" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD29" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A30" s="3">
         <v>0</v>
       </c>
@@ -2917,11 +3174,20 @@
       <c r="Z30" s="3">
         <v>0</v>
       </c>
-      <c r="AA30" s="3">
+      <c r="AA30" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB30" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC30" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD30" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A31" s="3">
         <v>0</v>
       </c>
@@ -3000,11 +3266,20 @@
       <c r="Z31" s="3">
         <v>0</v>
       </c>
-      <c r="AA31" s="3">
+      <c r="AA31" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB31" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC31" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD31" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A32" s="3">
         <v>0</v>
       </c>
@@ -3083,11 +3358,20 @@
       <c r="Z32" s="3">
         <v>0</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AA32" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB32" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC32" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD32" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A33" s="3">
         <v>0</v>
       </c>
@@ -3166,11 +3450,20 @@
       <c r="Z33" s="3">
         <v>0</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AA33" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB33" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC33" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD33" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A34" s="3">
         <v>0</v>
       </c>
@@ -3249,11 +3542,20 @@
       <c r="Z34" s="3">
         <v>0</v>
       </c>
-      <c r="AA34" s="3">
+      <c r="AA34" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB34" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC34" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD34" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A35" s="3">
         <v>0</v>
       </c>
@@ -3332,11 +3634,20 @@
       <c r="Z35" s="3">
         <v>0</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AA35" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB35" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC35" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD35" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A36" s="3">
         <v>0</v>
       </c>
@@ -3415,11 +3726,20 @@
       <c r="Z36" s="3">
         <v>0</v>
       </c>
-      <c r="AA36" s="3">
+      <c r="AA36" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB36" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC36" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD36" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A37" s="3">
         <v>0</v>
       </c>
@@ -3498,11 +3818,20 @@
       <c r="Z37" s="3">
         <v>0</v>
       </c>
-      <c r="AA37" s="3">
+      <c r="AA37" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB37" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC37" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD37" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A38" s="3">
         <v>0</v>
       </c>
@@ -3581,11 +3910,20 @@
       <c r="Z38" s="3">
         <v>0</v>
       </c>
-      <c r="AA38" s="3">
+      <c r="AA38" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB38" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC38" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD38" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A39" s="3">
         <v>0</v>
       </c>
@@ -3664,11 +4002,20 @@
       <c r="Z39" s="3">
         <v>0</v>
       </c>
-      <c r="AA39" s="3">
+      <c r="AA39" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB39" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC39" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD39" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A40" s="3">
         <v>0</v>
       </c>
@@ -3747,11 +4094,20 @@
       <c r="Z40" s="3">
         <v>0</v>
       </c>
-      <c r="AA40" s="3">
+      <c r="AA40" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB40" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC40" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD40" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A41" s="3">
         <v>0</v>
       </c>
@@ -3830,11 +4186,20 @@
       <c r="Z41" s="3">
         <v>0</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AA41" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB41" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC41" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD41" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A42" s="3">
         <v>0</v>
       </c>
@@ -3913,11 +4278,20 @@
       <c r="Z42" s="3">
         <v>0</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AA42" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB42" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC42" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD42" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A43" s="3">
         <v>0</v>
       </c>
@@ -3996,11 +4370,20 @@
       <c r="Z43" s="3">
         <v>0</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AA43" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB43" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC43" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD43" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A44" s="3">
         <v>0</v>
       </c>
@@ -4079,11 +4462,20 @@
       <c r="Z44" s="3">
         <v>0</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AA44" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB44" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC44" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD44" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A45" s="3">
         <v>0</v>
       </c>
@@ -4162,11 +4554,20 @@
       <c r="Z45" s="3">
         <v>0</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AA45" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB45" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC45" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD45" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A46" s="3">
         <v>0</v>
       </c>
@@ -4245,11 +4646,20 @@
       <c r="Z46" s="3">
         <v>0</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AA46" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB46" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC46" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD46" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A47" s="3">
         <v>0</v>
       </c>
@@ -4328,11 +4738,20 @@
       <c r="Z47" s="3">
         <v>0</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AA47" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB47" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC47" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD47" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A48" s="3">
         <v>0</v>
       </c>
@@ -4411,11 +4830,20 @@
       <c r="Z48" s="3">
         <v>0</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AA48" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB48" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC48" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD48" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A49" s="3">
         <v>0</v>
       </c>
@@ -4494,11 +4922,20 @@
       <c r="Z49" s="3">
         <v>0</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AA49" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB49" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC49" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD49" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A50" s="3">
         <v>0</v>
       </c>
@@ -4577,11 +5014,20 @@
       <c r="Z50" s="3">
         <v>0</v>
       </c>
-      <c r="AA50" s="3">
+      <c r="AA50" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB50" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC50" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD50" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A51" s="3">
         <v>0</v>
       </c>
@@ -4660,11 +5106,20 @@
       <c r="Z51" s="3">
         <v>0</v>
       </c>
-      <c r="AA51" s="3">
+      <c r="AA51" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB51" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC51" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD51" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A52" s="3">
         <v>0</v>
       </c>
@@ -4743,11 +5198,20 @@
       <c r="Z52" s="3">
         <v>0</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AA52" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB52" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC52" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD52" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A53" s="3">
         <v>0</v>
       </c>
@@ -4826,11 +5290,20 @@
       <c r="Z53" s="3">
         <v>0</v>
       </c>
-      <c r="AA53" s="3">
+      <c r="AA53" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB53" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC53" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD53" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A54" s="3">
         <v>0</v>
       </c>
@@ -4909,11 +5382,20 @@
       <c r="Z54" s="3">
         <v>0</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AA54" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB54" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC54" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD54" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A55" s="3">
         <v>0</v>
       </c>
@@ -4992,11 +5474,20 @@
       <c r="Z55" s="3">
         <v>0</v>
       </c>
-      <c r="AA55" s="3">
+      <c r="AA55" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB55" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC55" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD55" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A56" s="3">
         <v>0</v>
       </c>
@@ -5075,11 +5566,20 @@
       <c r="Z56" s="3">
         <v>0</v>
       </c>
-      <c r="AA56" s="3">
+      <c r="AA56" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB56" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC56" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD56" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A57" s="3">
         <v>0</v>
       </c>
@@ -5158,11 +5658,20 @@
       <c r="Z57" s="3">
         <v>0</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AA57" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB57" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC57" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD57" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A58" s="3">
         <v>0</v>
       </c>
@@ -5241,11 +5750,20 @@
       <c r="Z58" s="3">
         <v>0</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AA58" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB58" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC58" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD58" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A59" s="3">
         <v>0</v>
       </c>
@@ -5324,11 +5842,20 @@
       <c r="Z59" s="3">
         <v>0</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AA59" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB59" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC59" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD59" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A60" s="3">
         <v>0</v>
       </c>
@@ -5407,11 +5934,20 @@
       <c r="Z60" s="3">
         <v>0</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AA60" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB60" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC60" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD60" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A61" s="3">
         <v>0</v>
       </c>
@@ -5490,11 +6026,20 @@
       <c r="Z61" s="3">
         <v>0</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AA61" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB61" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC61" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD61" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A62" s="2">
         <f>A66-A67</f>
         <v>0</v>
@@ -5600,7 +6145,15 @@
         <v>0</v>
       </c>
       <c r="AA62" s="2">
-        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AB62" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC62" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD62" s="2">
         <v>0</v>
       </c>
     </row>

--- a/LDC.xlsx
+++ b/LDC.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://icrafcifor-my.sharepoint.com/personal/d_bodro_landscapealliance_org/Documents/Documents/GitHub/RegEco-BETIBEL-SOLUSI/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="8_{AD9C7155-FC41-450E-8731-B9FE4ACDF2E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4BA9F572-5CAF-405B-AB55-B7F750F07592}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="8_{AD9C7155-FC41-450E-8731-B9FE4ACDF2E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{52498B8B-85D5-41A3-9BC8-16FB724189A9}"/>
   <bookViews>
-    <workbookView xWindow="-28935" yWindow="-135" windowWidth="29070" windowHeight="15750" xr2:uid="{FDBA8644-8BAA-46FD-AFD9-3CA6C0ACD717}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" xr2:uid="{FDBA8644-8BAA-46FD-AFD9-3CA6C0ACD717}"/>
   </bookViews>
   <sheets>
     <sheet name="LDC" sheetId="1" r:id="rId1"/>
@@ -545,13 +545,13 @@
         <v>0</v>
       </c>
       <c r="I2" s="1">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="J2" s="2">
         <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="L2" s="2">
         <v>0</v>
@@ -566,13 +566,13 @@
         <v>0</v>
       </c>
       <c r="P2" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q2" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R2" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S2" s="2">
         <v>0</v>
@@ -637,20 +637,20 @@
         <v>0</v>
       </c>
       <c r="I3" s="1">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="J3" s="2">
         <v>0</v>
       </c>
       <c r="K3" s="1">
+        <v>0</v>
+      </c>
+      <c r="L3" s="2">
+        <v>0</v>
+      </c>
+      <c r="M3" s="2">
         <v>0.01</v>
       </c>
-      <c r="L3" s="2">
-        <v>0</v>
-      </c>
-      <c r="M3" s="2">
-        <v>0</v>
-      </c>
       <c r="N3" s="2">
         <v>0</v>
       </c>
@@ -661,7 +661,7 @@
         <v>0</v>
       </c>
       <c r="Q3" s="2">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="R3" s="2">
         <v>0</v>
@@ -670,7 +670,7 @@
         <v>0</v>
       </c>
       <c r="T3" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U3" s="2">
         <v>0</v>
@@ -717,7 +717,7 @@
         <v>0</v>
       </c>
       <c r="E4" s="1">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="F4" s="2">
         <v>0</v>
@@ -729,19 +729,19 @@
         <v>0</v>
       </c>
       <c r="I4" s="1">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="J4" s="2">
         <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="L4" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M4" s="2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="N4" s="2">
         <v>0</v>
@@ -753,7 +753,7 @@
         <v>0</v>
       </c>
       <c r="Q4" s="2">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="R4" s="2">
         <v>0</v>
@@ -833,10 +833,10 @@
         <v>0</v>
       </c>
       <c r="M5" s="1">
-        <v>1</v>
+        <v>0.01</v>
       </c>
       <c r="N5" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O5" s="2">
         <v>0</v>
@@ -845,7 +845,7 @@
         <v>0</v>
       </c>
       <c r="Q5" s="2">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="R5" s="2">
         <v>0</v>
@@ -901,7 +901,7 @@
         <v>0</v>
       </c>
       <c r="E6" s="1">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="F6" s="2">
         <v>0</v>
@@ -913,28 +913,28 @@
         <v>0</v>
       </c>
       <c r="I6" s="1">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="J6" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="L6" s="2">
         <v>0</v>
       </c>
       <c r="M6" s="2">
-        <v>0</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="N6" s="2">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="O6" s="1">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="P6" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q6" s="2">
         <v>0</v>
@@ -943,7 +943,7 @@
         <v>0</v>
       </c>
       <c r="S6" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T6" s="2">
         <v>0</v>
@@ -1011,7 +1011,7 @@
         <v>0</v>
       </c>
       <c r="K7" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7" s="2">
         <v>0</v>
@@ -1044,7 +1044,7 @@
         <v>0</v>
       </c>
       <c r="V7" s="1">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W7" s="2">
         <v>0</v>
@@ -1109,7 +1109,7 @@
         <v>0</v>
       </c>
       <c r="M8" s="2">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="N8" s="2">
         <v>0</v>
@@ -1127,7 +1127,7 @@
         <v>0</v>
       </c>
       <c r="S8" s="2">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="T8" s="2">
         <v>0</v>
@@ -1168,16 +1168,16 @@
         <v>0</v>
       </c>
       <c r="B9" s="1">
-        <v>7.0000000000000007E-2</v>
+        <v>0</v>
       </c>
       <c r="C9" s="1">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D9" s="2">
         <v>0</v>
       </c>
       <c r="E9" s="1">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="F9" s="2">
         <v>0</v>
@@ -1186,25 +1186,25 @@
         <v>0</v>
       </c>
       <c r="H9" s="1">
+        <v>0</v>
+      </c>
+      <c r="I9" s="2">
+        <v>0</v>
+      </c>
+      <c r="J9" s="2">
+        <v>1</v>
+      </c>
+      <c r="K9" s="2">
+        <v>0</v>
+      </c>
+      <c r="L9" s="2">
+        <v>0</v>
+      </c>
+      <c r="M9" s="2">
         <v>0.2</v>
       </c>
-      <c r="I9" s="2">
-        <v>0</v>
-      </c>
-      <c r="J9" s="2">
-        <v>0</v>
-      </c>
-      <c r="K9" s="2">
-        <v>0</v>
-      </c>
-      <c r="L9" s="2">
-        <v>0</v>
-      </c>
-      <c r="M9" s="2">
-        <v>0</v>
-      </c>
       <c r="N9" s="2">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="O9" s="2">
         <v>0</v>
@@ -1269,13 +1269,13 @@
         <v>0</v>
       </c>
       <c r="E10" s="1">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="F10" s="1">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="G10" s="1">
-        <v>7.0000000000000007E-2</v>
+        <v>0</v>
       </c>
       <c r="H10" s="2">
         <v>0</v>
@@ -1290,10 +1290,10 @@
         <v>0</v>
       </c>
       <c r="L10" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M10" s="2">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="N10" s="2">
         <v>0</v>
@@ -1332,7 +1332,7 @@
         <v>0</v>
       </c>
       <c r="Z10" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA10" s="2">
         <v>0</v>
@@ -1385,7 +1385,7 @@
         <v>0</v>
       </c>
       <c r="M11" s="3">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="N11" s="3">
         <v>0</v>
@@ -1504,7 +1504,7 @@
         <v>0</v>
       </c>
       <c r="V12" s="3">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W12" s="3">
         <v>0</v>
@@ -1596,7 +1596,7 @@
         <v>0</v>
       </c>
       <c r="V13" s="3">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="W13" s="3">
         <v>0</v>
@@ -1688,7 +1688,7 @@
         <v>0</v>
       </c>
       <c r="V14" s="3">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W14" s="3">
         <v>0</v>
@@ -1809,10 +1809,10 @@
     </row>
     <row r="16" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A16" s="3">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="B16" s="3">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="C16" s="3">
         <v>0</v>
@@ -1821,19 +1821,19 @@
         <v>0</v>
       </c>
       <c r="E16" s="3">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="F16" s="3">
         <v>0</v>
       </c>
       <c r="G16" s="3">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="H16" s="3">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="I16" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J16" s="3">
         <v>0</v>
@@ -1845,13 +1845,13 @@
         <v>0</v>
       </c>
       <c r="M16" s="3">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="N16" s="3">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="O16" s="3">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="P16" s="3">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="S16" s="3">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="T16" s="3">
         <v>0</v>
@@ -1982,13 +1982,13 @@
         <v>0</v>
       </c>
       <c r="AB17" s="2">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AC17" s="2">
         <v>0</v>
       </c>
       <c r="AD17" s="2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="18" spans="1:30" x14ac:dyDescent="0.3">
@@ -2062,7 +2062,7 @@
         <v>0</v>
       </c>
       <c r="X18" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y18" s="3">
         <v>0</v>
@@ -6041,120 +6041,94 @@
     </row>
     <row r="62" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A62" s="2">
-        <f>A66-A67</f>
-        <v>0</v>
+        <v>0.95</v>
       </c>
       <c r="B62" s="2">
-        <f t="shared" ref="B62:AA62" si="0">B66-B67</f>
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="C62" s="2">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D62" s="2">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E62" s="2">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="F62" s="2">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G62" s="2">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.97</v>
       </c>
       <c r="H62" s="2">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.95</v>
       </c>
       <c r="I62" s="2">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J62" s="2">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K62" s="2">
-        <f>K66-K67</f>
         <v>0</v>
       </c>
       <c r="L62" s="2">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="M62" s="2">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="N62" s="2">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="O62" s="2">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="P62" s="2">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="Q62" s="2">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R62" s="2">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S62" s="2">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="T62" s="2">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U62" s="2">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V62" s="2">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.69</v>
       </c>
       <c r="W62" s="2">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X62" s="2">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="Y62" s="2">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z62" s="2">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA62" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB62" s="2">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="AC62" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD62" s="2">
-        <v>0</v>
+        <v>0.99</v>
       </c>
     </row>
   </sheetData>
